--- a/校园招聘/制造业/消费电子／通信／智能设备/技术研发类/电气工程师/3_需重新出题/5轮_消费电子／通信／智能设备_电气工程师_需要重新出题.xlsx
+++ b/校园招聘/制造业/消费电子／通信／智能设备/技术研发类/电气工程师/3_需重新出题/5轮_消费电子／通信／智能设备_电气工程师_需要重新出题.xlsx
@@ -1,34 +1,254 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/risei/Downloads/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A8BE19-1D79-2D45-AF43-1FCAEC9685D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="5260" yWindow="760" windowWidth="19420" windowHeight="16600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="出题" sheetId="1" r:id="rId1"/>
+    <sheet name="出答案" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+  <si>
+    <t>问题</t>
+  </si>
+  <si>
+    <t>技能分类</t>
+  </si>
+  <si>
+    <t>技能</t>
+  </si>
+  <si>
+    <t>知识点</t>
+  </si>
+  <si>
+    <t>难度</t>
+  </si>
+  <si>
+    <t>行业</t>
+  </si>
+  <si>
+    <t>岗位</t>
+  </si>
+  <si>
+    <t>招聘场景</t>
+  </si>
+  <si>
+    <t>JD</t>
+  </si>
+  <si>
+    <t>提示词</t>
+  </si>
+  <si>
+    <t>当一个MCU接口需要驱动多个并联的数字输入引脚时，设计者有时会加入一个共射极晶体管作为驱动增强级。请简单说说，这个结构在这里主要解决了什么实际问题？</t>
+  </si>
+  <si>
+    <t>电路基础</t>
+  </si>
+  <si>
+    <t>模拟电路分析</t>
+  </si>
+  <si>
+    <t>共射共集放大电路特性</t>
+  </si>
+  <si>
+    <t>中等</t>
+  </si>
+  <si>
+    <t>消费电子/通信/智能设备</t>
+  </si>
+  <si>
+    <t>电气工程师</t>
+  </si>
+  <si>
+    <t>校园招聘/社会招聘通用</t>
+  </si>
+  <si>
+    <t>电气：
+一、岗位通用职责
+1. 硬件方案设计与原理图输出
+根据产品需求完成电气/硬件方案设计、原理图绘制、模块电路设计与技术评审；校招/初级侧重读图、绘制常规电路原理图和协助方案整理，1-3年侧重独立完成模块电路设计，3-5年侧重整机硬件架构定义、指标分解与方案评审。
+2. 电路原理分析与器件选型
+理解供电、信号链、接口、保护等电路的工作原理、信号流向与关键参数，完成电子元器件选型、Datasheet 评估与 BOM 输出；校招/初级侧重识别主要电路模块与基础器件参数，1-3年侧重按电路原理判断异常来源并完成常规选型，3-5年侧重从原理层面分析瓶颈、故障根因与降本替代方向。
+3. 样机调试、测试与故障定位
+参与新产品、改版样机及试产板的上电、功能调试、性能测试和问题定位与优化；校招/初级侧重协助焊接、调试与测试记录，1-3年侧重独立处理常见硬件问题，3-5年侧重制定调试方案、疑难/偶发问题根因分析和整改闭环。
+4. 设计文档与硬件技术档案管理
+建立并维护原理图/PCB 资料、BOM 清单、器件归一化清单、设计文档、测试规范与版本履历，根据问题频率与器件关键度优化选型与替代策略，支撑研发协同与量产追溯。
+二、方向职责
+方向一：电源与电路设计方向
+1. 完成产品供电方案、开关电源拓扑设计、控制环路与功率/磁性器件选型，满足效率、纹波、温升等指标。
+2. 进行电源指标优化、低功耗与电源管理设计，处理量产中的电源相关问题。
+方向二：PCB与信号完整性方向
+1. 完成 PCB 布局布线、叠层与阻抗控制、高速接口设计与信号/电源完整性处理。
+2. 推进可制造性设计与生产文件输出，配合解决 SI/PI 及布线相关问题。
+方向三：机电接口与系统集成方向
+1. 完成 MCU/SoC 最小系统、通信接口、通信模组/射频天线、传感器与连接器等接口设计。
+2. 推进软硬件联调与系统集成，配合解决接口兼容与系统级问题。
+方向四：EMC、认证与可靠性方向
+1. 完成 EMC/EMI 预测试与整改、ESD 与防护设计、安规与认证测试（CE/FCC/3C/UL）。
+2. 推进环境可靠性试验、降额与稳健设计，确保产品满足国内外标准与可靠性要求。
+方向五：调试验证与量产导入方向
+1. 跟进样机功能验证、性能测试，制定测试规范与测试方案。
+2. 推进试产与量产导入（NPI），完成量产不良根因分析与整改闭环。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"你是一位经验丰富的资深面试官，拥有超过 10 年人才招聘经验。你尤其擅长从知识深度、逻辑思维以及实战能力等多个维度全面评估候选人。
+现在请依据以下要求，为【{{industry}}】行业下的【{{job}}】岗位的候选人精心准备【{{num}}】道视频面试题。
+关于目标行业下岗位的岗位描述：【{{JD}}】
+## 面试题要求
+- 题目类型：必须为简答题。
+- 内容相关性：题目内容要紧密围绕【{{category}}】技能分类下【{{skill}}】技能里的【{{knowledge}}】知识点展开。
+- 行业岗位适用性：题目需与【{{industry}}】行业下的【{{job}}】岗位职责高度适配，贴合该行业实际情况。
+- 招聘场景：题目应契合【{{scene}}】这一特定招聘场景。
+- 题目难度：全部设定为【{{level}}】难度，具体难度定义如下：
+    · 简单：考察应聘者能否识别、回忆出关键概念，是否了解关键概念背后的基本原理。提问需从小而具体的切入点考察对某知识点的概念识别与规则理解，无场景，纯理论考察。如“请简述什么是负载均衡技术中轮询策略”。建议作答时间控制在60秒内。字数控制在10～30字。
+    · 中等：考察应聘者是否知道在一个简单应用场景下用何种方法解决问题，解决机制是什么。提问内容涉及概念与规则的基础应用，场景是这个知识点常见的简单应用场景，禁止涉及穷举、优劣势分析、系统性设计或冲突情况。如“当一个服务有多个实例时，负载均衡器是怎么判断某个实例‘可用’从而把请求转发过去的？”建议作答时间控制在90秒内。字数控制在30～60字。
+    · 困难：考察应聘者是否知道在复杂/业务场景下如何运用知识点进行系统设计或优化来解决问题。提问内容涉及通过多规则整合进行复杂问题解决，需要候选人分析多方面的因素，权衡不同的选择，提出解决方案，并清晰阐述决策的依据和逻辑。场景应是较为复杂的业务场景。如“线上服务在高峰期出现部分用户延迟很高，但监控显示整体 CPU 并不高，你怀疑是负载均衡分配不均导致的。你会如何定位问题，并调整负载均衡策略来改善长尾延迟？” 。建议作答时间控制在120秒内。字数控制在60～90字。
+- 题干长度：一个题目里只能有1个小问，禁止连环提问！使读题时间控制在30秒内，难度越低的题题干应越好理解。
+-易答性：
+1.禁用词：写代码、写出、编写、绘制、计算等一些口头无法表述的内容，确保候选人仅通过口头回答即可完成答题；
+2.不能出现让候选人讲述某一个软件的操作步骤；
+3.提问应该逻辑严谨，简单易懂，提出问题时需要模仿面试官在面试的口吻，不能过于生硬而让候选人不能明白题目的意思；
+4.编程题要给出规定的编程语言。
+- 内容限制：
+1.问题中的应用场景/条件不能是虚构的或者故事化的场景。语言上，类似“假设....”的提问是不被允许的。
+2.技术时效性：题干禁止问旧版本/早期版本的技术，涉及的技术场景必须是2022年之后在用的，但不必在题干中标注年份。
+3.问题中不能出现【{{industry}}】行业名称、【{{scene}}】特定招聘场景名称、【{{job}}】职位
+4.对于【通用行业】的知识点提问需要通用化，业务场景需要是各行各业的应聘者都能看懂的。
+5.所有的问题都是知识点面试问题，不能出行为化面试题
+6.尽量不要出现英文，能用中文的用中文表达！
+7.禁止出现事实、知识错误！
+8.禁止出现“请用一句话回答”这类强势粗暴的提问方法，可以说“请简述”“请简单说说”等
+## 输出规范要求
+- 若题目数量超过 1 道，要保证所有题目内容不重复，从不同主题或提问角度进行设计。
+- 严格以规范的 JSON 格式输出结果，不包含任何额外的文本说明。
+## 输出示例
+{{
+    ""questions"": [{{
+        ""question"": ""题目题干""，
+        ""level"": ""难度"",
+        ""time"": 建议答题时间，整数类型
+    }}]
+}}"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"电气：
+一、岗位通用职责
+1. 硬件方案设计与原理图输出
+根据产品需求完成电气/硬件方案设计、原理图绘制、模块电路设计与技术评审；校招/初级侧重读图、绘制常规电路原理图和协助方案整理，1-3年侧重独立完成模块电路设计，3-5年侧重整机硬件架构定义、指标分解与方案评审。
+2. 电路原理分析与器件选型
+理解供电、信号链、接口、保护等电路的工作原理、信号流向与关键参数，完成电子元器件选型、Datasheet 评估与 BOM 输出；校招/初级侧重识别主要电路模块与基础器件参数，1-3年侧重按电路原理判断异常来源并完成常规选型，3-5年侧重从原理层面分析瓶颈、故障根因与降本替代方向。
+3. 样机调试、测试与故障定位
+参与新产品、改版样机及试产板的上电、功能调试、性能测试和问题定位与优化；校招/初级侧重协助焊接、调试与测试记录，1-3年侧重独立处理常见硬件问题，3-5年侧重制定调试方案、疑难/偶发问题根因分析和整改闭环。
+4. 设计文档与硬件技术档案管理
+建立并维护原理图/PCB 资料、BOM 清单、器件归一化清单、设计文档、测试规范与版本履历，根据问题频率与器件关键度优化选型与替代策略，支撑研发协同与量产追溯。
+二、方向职责
+方向一：电源与电路设计方向
+1. 完成产品供电方案、开关电源拓扑设计、控制环路与功率/磁性器件选型，满足效率、纹波、温升等指标。
+2. 进行电源指标优化、低功耗与电源管理设计，处理量产中的电源相关问题。
+方向二：PCB与信号完整性方向
+1. 完成 PCB 布局布线、叠层与阻抗控制、高速接口设计与信号/电源完整性处理。
+2. 推进可制造性设计与生产文件输出，配合解决 SI/PI 及布线相关问题。
+方向三：机电接口与系统集成方向
+1. 完成 MCU/SoC 最小系统、通信接口、通信模组/射频天线、传感器与连接器等接口设计。
+2. 推进软硬件联调与系统集成，配合解决接口兼容与系统级问题。
+方向四：EMC、认证与可靠性方向
+1. 完成 EMC/EMI 预测试与整改、ESD 与防护设计、安规与认证测试（CE/FCC/3C/UL）。
+2. 推进环境可靠性试验、降额与稳健设计，确保产品满足国内外标准与可靠性要求。
+方向五：调试验证与量产导入方向
+1. 跟进样机功能验证、性能测试，制定测试规范与测试方案。
+2. 推进试产与量产导入（NPI），完成量产不良根因分析与整改闭环。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你是一位经验丰富的资深面试官，拥有超过 10 年人才招聘经验。你尤其擅长从知识深度、逻辑思维以及实战能力等多个维度全面评估候选人。
+现在请依据以下要求，为面试【{{job}}】职位的候选人的视频面试题【{{Q}}】生成符合规则的参考答案。
+## 参考答案要求
+- 内容相关性：题目内容要紧密围绕【{{category}}】技能分类下【{{skill}}】技能里的【{{knowledge}}】知识点展开。
+- 岗位适用性：答案需与【{{{industry}}】行业的【{{job}}】岗位的工作范畴高度适配，仅从该岗位工作内容角度生成。禁止从技术的口径回答问题！！岗位工作内容参考：【{{JD}}】
+- 使用场景：答案应契合【{{scene}}】这一特定使用场景。
+- 内容与格式：每个题目的三层参考答案字数合计限制在300～600字，每个题目考察的都是一个岗位上某个技能的掌握程度，掌握程度分为以下三个层次，因此参考答案也需要分层生成。对第一层给出回答题干所需的基础知识，内容严格对应题干，不要举例，不要超出题干所问的范围！对第二层给出这个应用场景下常见的2～4种技术方案或方法的分析，优劣势分别是什么，哪种最好，方法要在保证时效性的基础上全面！分析要深入！对第三层给出这个知识点或场景下最最常出现的1个异常情况和1个复杂问题，以及每种情况的解决思路，输出时要结构化！小标题结构为：1个异常情况概要，具体情况，解决思路；1个复杂问题概要，具体问题，解决思路。
+参考答案约束：
+1.参考答案的内容必须严格对应岗位口径
+2.禁止出现代码块、符号等书面表达，所有类似内容必须用口语自然语言描述的形式代替
+3.禁止出现公式、计算等
+4.能用中文的用中文表达
+5.涉及的技术方法必须是2023年之后在用的，但相关时间信息不必出现在答案文本中
+6.禁止出现知识、事实错误！！
+常见的错误清单：{把相近概念混为一谈
+把局部实现写成通用规律
+把适用条件说错或漏掉前提
+把可选方案写成唯一答案
+数学/统计结论直接上升为业务结论
+边界值、分类、覆盖率类题目只答一半
+举例本身错误
+绝对化、法条化、一刀切表述
+业务场景包装过重，压坏技术口径}
+## 输出示例
+{{
+    "questions": [{{
+        "question": "题目题干"，
+        "answer1":"参考答案-第一层",
+        "answer2":"参考答案-第二层",
+        "answer3":"参考答案-第三层"
+    }}]
+}}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="4"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,81 +266,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,141 +578,103 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>问题</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>第一层</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>第二层</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>第三层</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>技能分类</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>知识点</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>难度</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>行业</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>岗位</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>招聘场景</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>JD</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>提示词</t>
-        </is>
+    <row r="1" spans="1:10">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>当一个MCU接口需要驱动多个并联的数字输入引脚时，设计者有时会加入一个共射极晶体管作为驱动增强级。请简单说说，这个结构在这里主要解决了什么实际问题？</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>这个结构主要解决MCU GPIO引脚输出驱动能力不足的问题，即当多个数字输入器件并联接入同一MCU引脚时，总输入电流需求可能超过MCU引脚允许的最大灌电流或拉电流，导致电平不稳定、响应延迟甚至引脚损坏。</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>在消费电子、通信和智能设备硬件设计中，常见替代方案有三种：一是直接用MCU引脚驱动，成本低但受限于手册标称的绝对最大电流和推荐工作电流，易引发批量试产失效；二是改用专用缓冲器芯片，如74LVC系列，驱动能力强且信号完整性好，但增加BOM成本和PCB面积；三是采用共射极NPN晶体管（基极限流电阻+集电极上拉），结构简洁、成本极低、兼容性强，特别适合对成本敏感且IO资源紧张的终端产品。综合时效性、量产可行性与设计鲁棒性，共射极晶体管方案在中小批量、快速迭代的智能硬件项目中仍是首选，尤其适用于按键矩阵、LED指示灯使能、传感器使能等低速但多负载场景。</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1个异常情况概要：MCU引脚电平被拉低后无法恢复高电平。具体情况是多个CMOS输入并联导致总输入漏电流叠加，超出MCU上拉能力，实测高电平跌至2.1V以下，造成下游器件识别为低电平。解决思路是核查所有并联输入端的静态漏电流参数，确认是否超限，并在MCU侧增设共射极晶体管，将驱动任务从MCU IO转移至三极管集电极回路，确保驱动能力冗余。1个复杂问题概要：共射电路引入开关延迟与振荡风险。具体问题是晶体管基极未加下拉电阻，在MCU复位期间出现悬空，导致下游电路误触发或功耗异常。解决思路是在基极与GND间添加10kΩ下拉电阻，同时结合MCU启动时序检查，确保驱动信号在系统初始化完成前处于确定态，该做法已纳入主流智能设备硬件设计checklist。</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>电路基础</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>模拟电路分析</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>共射共集放大电路特性</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>消费电子/通信/智能设备</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>电气工程师</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+    <row r="2" spans="1:10" ht="409.6">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B304D94A-4D75-6746-8711-E43855FF4A65}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="409.6">
+      <c r="A2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>